--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/UNIFICACION/ANDRES/_SALIDA/reporte_ANDRES.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/UNIFICACION/ANDRES/_SALIDA/reporte_ANDRES.xlsx
@@ -701,7 +701,7 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Generado: 18/03/2026  15:51</t>
+          <t>Generado: 24/03/2026  15:10</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Pos 3
-Obligaciones Grales y Especificas</t>
+Obligaciones Generales y Especificas</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="U3" s="6" t="inlineStr">
         <is>
+          <t>Pos 13c
+Plantilla Visita (Efectiva)</t>
+        </is>
+      </c>
+      <c r="V3" s="6" t="inlineStr">
+        <is>
           <t>Pos 13b
 Soporte Visita (Efectiva)</t>
-        </is>
-      </c>
-      <c r="V3" s="6" t="inlineStr">
-        <is>
-          <t>Pos 13c
-Plantilla Visita (Efectiva)</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">

--- a/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/UNIFICACION/ANDRES/_SALIDA/reporte_ANDRES.xlsx
+++ b/SCRIPT_PDFS/SCRIPS_DOCUMENTADOS/UNIFICACION/ANDRES/_SALIDA/reporte_ANDRES.xlsx
@@ -124,7 +124,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -144,6 +144,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007D4E00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006A1B4D"/>
       </patternFill>
     </fill>
     <fill>
@@ -198,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -221,16 +226,19 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -242,19 +250,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -272,7 +280,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,6 +290,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -649,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM19"/>
+  <dimension ref="A1:AP19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -684,13 +695,16 @@
     <col width="11" customWidth="1" min="30" max="30"/>
     <col width="11" customWidth="1" min="31" max="31"/>
     <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="22" customWidth="1" min="33" max="33"/>
-    <col width="9" customWidth="1" min="34" max="34"/>
-    <col width="15" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
-    <col width="11" customWidth="1" min="37" max="37"/>
-    <col width="8" customWidth="1" min="38" max="38"/>
-    <col width="55" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="9" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="8" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="55" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -701,7 +715,7 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Generado: 24/03/2026  15:10</t>
+          <t>Generado: 25/03/2026  10:27</t>
         </is>
       </c>
     </row>
@@ -851,1139 +865,1231 @@
       </c>
       <c r="Y3" s="7" t="inlineStr">
         <is>
+          <t>Pos 13f
+Carátula Consumo</t>
+        </is>
+      </c>
+      <c r="Z3" s="7" t="inlineStr">
+        <is>
+          <t>Pos 13g
+Acta de Consumo</t>
+        </is>
+      </c>
+      <c r="AA3" s="8" t="inlineStr">
+        <is>
           <t>Pos 14
 Carátula Comunicación</t>
         </is>
       </c>
-      <c r="Z3" s="7" t="inlineStr">
+      <c r="AB3" s="8" t="inlineStr">
         <is>
           <t>Pos 16a
 Carátula Otros (sección final)</t>
         </is>
       </c>
-      <c r="AA3" s="6" t="inlineStr">
+      <c r="AC3" s="6" t="inlineStr">
         <is>
           <t>Pos 16b
 Pantallazo SARLAFT</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr">
+      <c r="AD3" s="4" t="inlineStr">
         <is>
           <t>Pos 17
 RIPS</t>
         </is>
       </c>
-      <c r="AC3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>Pos 18
 Indicadores de Calidad del Prestador</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>Pos 19
 Eventos Adversos</t>
         </is>
       </c>
-      <c r="AE3" s="7" t="inlineStr">
+      <c r="AG3" s="8" t="inlineStr">
         <is>
           <t>Comunicaciones
 (todas)</t>
         </is>
       </c>
-      <c r="AF3" s="7" t="inlineStr">
+      <c r="AH3" s="8" t="inlineStr">
         <is>
           <t>Otros
 (todos)</t>
         </is>
       </c>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="AI3" s="3" t="inlineStr">
         <is>
           <t>ESTADO</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AJ3" s="3" t="inlineStr">
         <is>
           <t>VISITA</t>
         </is>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
+      <c r="AK3" s="3" t="inlineStr">
         <is>
           <t>TIPO VISITA</t>
         </is>
       </c>
-      <c r="AJ3" s="3" t="inlineStr">
+      <c r="AL3" s="3" t="inlineStr">
         <is>
           <t>CALIDAD</t>
         </is>
       </c>
-      <c r="AK3" s="3" t="inlineStr">
+      <c r="AM3" s="3" t="inlineStr">
         <is>
           <t>PROT/ORT</t>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AN3" s="3" t="inlineStr">
         <is>
           <t>PILA</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CONSUMO</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>INFORME 11 DICIEMBRE-2025 0222-2025</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Q4" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R4" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="V4" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="W4" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X4" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y4" s="9" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="T4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="V4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X4" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y4" s="10" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="Z4" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AA4" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="AA4" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="AB4" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AC4" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AD4" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AE4" s="9" t="inlineStr">
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AC4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AD4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF4" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG4" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="inlineStr">
+      <c r="AH4" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG4" s="11" t="inlineStr">
+      <c r="AI4" s="12" t="inlineStr">
         <is>
           <t>Unificado Incompleto</t>
         </is>
       </c>
-      <c r="AH4" s="12" t="inlineStr">
+      <c r="AJ4" s="13" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="AI4" s="13" t="inlineStr">
+      <c r="AK4" s="14" t="inlineStr">
         <is>
           <t>EFECTIVA</t>
         </is>
       </c>
-      <c r="AJ4" s="12" t="inlineStr">
+      <c r="AL4" s="13" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="AK4" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AL4" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AM4" s="15" t="inlineStr"/>
+      <c r="AM4" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AN4" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AO4" s="16" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AP4" s="17" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>INFORME 12 DICIEMBRE-2025 0215-2024</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Q5" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R5" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="T5" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V5" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W5" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X5" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y5" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Z5" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V5" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X5" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y5" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="AA5" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="AB5" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AC5" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AD5" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AE5" s="9" t="inlineStr">
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF5" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG5" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF5" s="10" t="inlineStr">
+      <c r="AH5" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG5" s="17" t="inlineStr">
+      <c r="AI5" s="19" t="inlineStr">
         <is>
           <t>Unificado Completo</t>
         </is>
       </c>
-      <c r="AH5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AI5" s="18" t="inlineStr">
+      <c r="AJ5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AK5" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AJ5" s="12" t="inlineStr">
+      <c r="AL5" s="13" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="AK5" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AL5" s="19" t="inlineStr">
+      <c r="AM5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AN5" s="16" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="AM5" s="15" t="inlineStr">
+      <c r="AO5" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP5" s="17" t="inlineStr">
         <is>
           <t>Sin posición: 0215-2025 EVENTO .pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>INFORME 12 DICIEMBRE-2025 0662-2024</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Q6" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R6" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="T6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U6" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V6" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W6" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Y6" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Z6" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="T6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U6" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V6" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X6" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="Y6" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z6" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="AA6" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="AB6" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AC6" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AD6" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AE6" s="9" t="inlineStr">
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD6" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE6" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF6" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG6" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF6" s="10" t="inlineStr">
+      <c r="AH6" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG6" s="11" t="inlineStr">
+      <c r="AI6" s="12" t="inlineStr">
         <is>
           <t>Unificado Incompleto</t>
         </is>
       </c>
-      <c r="AH6" s="12" t="inlineStr">
+      <c r="AJ6" s="13" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="AI6" s="20" t="inlineStr">
+      <c r="AK6" s="21" t="inlineStr">
         <is>
           <t>INASISTENCIA</t>
         </is>
       </c>
-      <c r="AJ6" s="12" t="inlineStr">
+      <c r="AL6" s="13" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="AK6" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AL6" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AM6" s="15" t="inlineStr">
+      <c r="AM6" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AN6" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AO6" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP6" s="17" t="inlineStr">
         <is>
           <t>Sin posición: 0662-2024 SOPORTE DE MEDICION .pdf, INFORME DE PAGO-0662-2024.pdf  [dup pos 7]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>INFORME 12 DICIEMBRE-2025 0739-2024</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Q7" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R7" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S7" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="T7" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U7" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W7" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="X7" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="Q7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="T7" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U7" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="X7" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y7" s="10" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
       <c r="Z7" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="AA7" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="AB7" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AC7" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AD7" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AE7" s="9" t="inlineStr">
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF7" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG7" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF7" s="10" t="inlineStr">
+      <c r="AH7" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG7" s="17" t="inlineStr">
+      <c r="AI7" s="19" t="inlineStr">
         <is>
           <t>Unificado Completo</t>
         </is>
       </c>
-      <c r="AH7" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AI7" s="18" t="inlineStr">
+      <c r="AJ7" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AK7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AJ7" s="12" t="inlineStr">
+      <c r="AL7" s="13" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="AK7" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AL7" s="19" t="inlineStr">
+      <c r="AM7" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AN7" s="16" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="AM7" s="15" t="inlineStr"/>
+      <c r="AO7" s="16" t="inlineStr">
+        <is>
+          <t>SÍ</t>
+        </is>
+      </c>
+      <c r="AP7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>INFORME 12 DICIEMBRE-2025 0910-2024</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="L8" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="O8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="P8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Q8" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="R8" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="S8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="T8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U8" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V8" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="X8" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Y8" s="9" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="Z8" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="Q8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="T8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U8" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V8" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W8" s="10" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="X8" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Y8" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Z8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="AA8" s="10" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="AB8" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="AC8" s="11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AD8" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AE8" s="9" t="inlineStr">
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AD8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF8" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG8" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF8" s="10" t="inlineStr">
+      <c r="AH8" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AG8" s="17" t="inlineStr">
+      <c r="AI8" s="19" t="inlineStr">
         <is>
           <t>Unificado Completo</t>
         </is>
       </c>
-      <c r="AH8" s="12" t="inlineStr">
+      <c r="AJ8" s="13" t="inlineStr">
         <is>
           <t>SÍ</t>
         </is>
       </c>
-      <c r="AI8" s="21" t="inlineStr">
+      <c r="AK8" s="22" t="inlineStr">
         <is>
           <t>ESCALAMIENTO</t>
         </is>
       </c>
-      <c r="AJ8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AK8" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AL8" s="14" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="AM8" s="15" t="inlineStr">
+      <c r="AL8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AM8" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AN8" s="15" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AO8" s="20" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AP8" s="17" t="inlineStr">
         <is>
           <t>Sin posición: 0910-2024 COMUNICADO_2.pdf, 0910-2024 SOPORTE DE MEDICION .pdf</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>RESUMEN</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Total     : 5</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Completos : 3</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>Incomp.   : 2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Error     : 0</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>LEYENDA:</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>Presente y unificado</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t>Faltante</t>
         </is>
       </c>
-      <c r="F17" s="29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G17" s="28" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" s="29" t="inlineStr">
         <is>
           <t>No aplica</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Grupos:</t>
         </is>
@@ -1993,37 +2099,47 @@
           <t>Siempre</t>
         </is>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>Obligatorio en todos los informes</t>
         </is>
       </c>
-      <c r="D19" s="30" t="inlineStr">
+      <c r="D19" s="31" t="inlineStr">
         <is>
           <t>Calidad</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="29" t="inlineStr">
         <is>
           <t>Solo si hay medición de calidad (5a/5b/5c)</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr">
+      <c r="F19" s="32" t="inlineStr">
         <is>
           <t>Visita</t>
         </is>
       </c>
-      <c r="G19" s="28" t="inlineStr">
+      <c r="G19" s="29" t="inlineStr">
         <is>
           <t>Solo si hubo visita (efectiva/escalamiento/inasistencia)</t>
         </is>
       </c>
-      <c r="H19" s="32" t="inlineStr">
+      <c r="H19" s="33" t="inlineStr">
+        <is>
+          <t>Consumo</t>
+        </is>
+      </c>
+      <c r="I19" s="29" t="inlineStr">
+        <is>
+          <t>Solo si hay Acta de Consumo (13f carátula + 13g acta)</t>
+        </is>
+      </c>
+      <c r="J19" s="34" t="inlineStr">
         <is>
           <t>Com/Otros</t>
         </is>
       </c>
-      <c r="I19" s="28" t="inlineStr">
+      <c r="K19" s="29" t="inlineStr">
         <is>
           <t>Comunicaciones y Otros (archivos múltiples)</t>
         </is>
